--- a/public/content/portfolio.xlsx
+++ b/public/content/portfolio.xlsx
@@ -3,14 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="instructions" sheetId="1" r:id="rId1"/>
-    <sheet name="profile" sheetId="2" r:id="rId2"/>
-    <sheet name="nav" sheetId="3" r:id="rId3"/>
-    <sheet name="social" sheetId="4" r:id="rId4"/>
-    <sheet name="skills" sheetId="5" r:id="rId5"/>
-    <sheet name="services" sheetId="6" r:id="rId6"/>
-    <sheet name="projects" sheetId="7" r:id="rId7"/>
-    <sheet name="credits" sheetId="8" r:id="rId8"/>
+    <sheet name="profile" sheetId="1" r:id="rId1"/>
+    <sheet name="nav" sheetId="2" r:id="rId2"/>
+    <sheet name="services" sheetId="3" r:id="rId3"/>
+    <sheet name="builds" sheetId="4" r:id="rId4"/>
+    <sheet name="team" sheetId="5" r:id="rId5"/>
+    <sheet name="process" sheetId="6" r:id="rId6"/>
+    <sheet name="why" sheetId="7" r:id="rId7"/>
+    <sheet name="social" sheetId="8" r:id="rId8"/>
+    <sheet name="credits" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -404,89 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B27"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>sheet</v>
-      </c>
-      <c r="B1" t="str">
-        <v>how_to_edit</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>profile</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Key/value rows. Change greeting, title, bio, highlight word, location, email, and links. Title can include a line break with \n.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>nav</v>
-      </c>
-      <c r="B3" t="str">
-        <v>One row per menu item. href is a page section id like #home. icon is home, projects, or contact.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>social</v>
-      </c>
-      <c r="B4" t="str">
-        <v>One row per social button. icon is github, linkedin, or email. Put the full URL (or mailto:).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>skills</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Tech marquee. name is the label. icon is a file in public/svg (example: react.svg).</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>services</v>
-      </c>
-      <c r="B6" t="str">
-        <v>What I do accordion. Repeat the same category on multiple rows. icon is web, mobile, or design.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>projects</v>
-      </c>
-      <c r="B7" t="str">
-        <v>One row per project. image can be a URL or /images/file.jpg in public. github and preview are links.</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>credits</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Footer “built with” lines. icon is a file in public/svg.</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
-  <cols>
-    <col min="1" max="1" width="21.83203125" customWidth="1"/>
-    <col min="2" max="2" width="80.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="63.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -499,195 +421,225 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>name</v>
+        <v>logo</v>
       </c>
       <c r="B2" t="str">
-        <v>Your Name</v>
+        <v>LOGO</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>greeting</v>
+        <v>name</v>
       </c>
       <c r="B3" t="str">
-        <v>Hi, I'm Your Name</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
+        <v>Studio</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="str">
-        <v>title</v>
-      </c>
-      <c r="B4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Software
-Developer</v>
+        <v>site_title</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Studio | We build digital products</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bio</v>
+        <v>hero_title</v>
       </c>
       <c r="B5" t="str">
-        <v>Transforming ideas into interactive and seamless digital experiences with cutting-edge {highlight} development.</v>
+        <v>WE BUILD DIGITAL PRODUCTS</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>highlight</v>
+        <v>hero_tags</v>
       </c>
       <c r="B6" t="str">
-        <v>frontend</v>
+        <v>Mobile • Web • Backend • AI</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>location</v>
+        <v>hero_cta</v>
       </c>
       <c r="B7" t="str">
-        <v>Your country</v>
+        <v>Start a Project</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>email</v>
+        <v>services_heading</v>
       </c>
       <c r="B8" t="str">
-        <v>hello@example.com</v>
+        <v>SERVICES</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>site_title</v>
+        <v>builds_heading</v>
       </c>
       <c r="B9" t="str">
-        <v>Your Name | Portfolio</v>
+        <v>WHAT WE CAN BUILD</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>projects_kicker</v>
+        <v>team_heading</v>
       </c>
       <c r="B10" t="str">
-        <v>My work</v>
+        <v>OUR TEAM</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>projects_heading</v>
+        <v>process_heading</v>
       </c>
       <c r="B11" t="str">
-        <v>Projects</v>
+        <v>HOW WE WORK</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>more_projects_label</v>
+        <v>why_heading</v>
       </c>
       <c r="B12" t="str">
-        <v>More projects on</v>
+        <v>WHY US</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>more_projects_url</v>
+        <v>cta_title</v>
       </c>
       <c r="B13" t="str">
-        <v>https://github.com</v>
+        <v>HAVE AN IDEA?</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>contact_kicker</v>
+        <v>cta_subtitle</v>
       </c>
       <c r="B14" t="str">
-        <v>Let's talk</v>
+        <v>LET'S BUILD IT.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>contact_heading</v>
+        <v>cta_button</v>
       </c>
       <c r="B15" t="str">
-        <v>Contact</v>
+        <v>Contact Us</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>contact_text</v>
+        <v>location</v>
       </c>
       <c r="B16" t="str">
-        <v>Have a question or a project in mind? Feel free to reach out.</v>
+        <v>Ameerpet, Hyderabad, 500016</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>form_endpoint</v>
+        <v>mobile</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>7095399332, 7381277084</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>form_success</v>
+        <v>email</v>
       </c>
       <c r="B18" t="str">
-        <v>Thank you for your message!</v>
+        <v>hello@example.com</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>services_heading</v>
+        <v>contact_kicker</v>
       </c>
       <c r="B19" t="str">
-        <v>What I do?</v>
+        <v>Let's talk</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>copyright_name</v>
+        <v>contact_heading</v>
       </c>
       <c r="B20" t="str">
-        <v>Your Name</v>
+        <v>Contact</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>copyright_credit</v>
+        <v>contact_text</v>
       </c>
       <c r="B21" t="str">
-        <v>Andres Hernandez</v>
+        <v>Have a question or a project in mind? Feel free to reach out.</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>distributed_by</v>
+        <v>form_endpoint</v>
       </c>
       <c r="B22" t="str">
-        <v>ThemeWagon</v>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
+        <v>form_success</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Thank you for your message!</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>copyright_name</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Studio</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>copyright_credit</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>distributed_by</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>distributed_url</v>
       </c>
-      <c r="B23" t="str">
-        <v>https://themewagon.com</v>
+      <c r="B27" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B27"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B5"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,51 +649,340 @@
       <c r="B1" t="str">
         <v>href</v>
       </c>
-      <c r="C1" t="str">
-        <v>icon</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Home</v>
+        <v>Services</v>
       </c>
       <c r="B2" t="str">
-        <v>#home</v>
-      </c>
-      <c r="C2" t="str">
-        <v>home</v>
+        <v>#services</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Projects</v>
+        <v>Team</v>
       </c>
       <c r="B3" t="str">
-        <v>#projects</v>
-      </c>
-      <c r="C3" t="str">
-        <v>projects</v>
+        <v>#team</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>About</v>
+      </c>
+      <c r="B4" t="str">
+        <v>#about</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>Contact</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>#contact</v>
-      </c>
-      <c r="C4" t="str">
-        <v>contact</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <cols>
+    <col min="1" max="1" width="9.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>icon</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Mobile</v>
+      </c>
+      <c r="B2" t="str">
+        <v>mobile</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Web</v>
+      </c>
+      <c r="B3" t="str">
+        <v>web</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Backend</v>
+      </c>
+      <c r="B4" t="str">
+        <v>backend</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AI</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ai</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>APIs</v>
+      </c>
+      <c r="B6" t="str">
+        <v>api</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>UI/UX</v>
+      </c>
+      <c r="B7" t="str">
+        <v>design</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>icon</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Apps</v>
+      </c>
+      <c r="B2" t="str">
+        <v>mobile</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>E-commerce</v>
+      </c>
+      <c r="B3" t="str">
+        <v>shop</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="B4" t="str">
+        <v>booking</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Delivery</v>
+      </c>
+      <c r="B5" t="str">
+        <v>delivery</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Business</v>
+      </c>
+      <c r="B6" t="str">
+        <v>business</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AI</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ai</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="3" max="3" width="7.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>role</v>
+      </c>
+      <c r="C1" t="str">
+        <v>photo</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Deekshith Chakilam</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Rajesh Swain</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Developer</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B6"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>step</v>
+      </c>
+      <c r="B1" t="str">
+        <v>label</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Discuss</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Plan</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Design</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Build</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Launch</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A5"/>
+  <cols>
+    <col min="1" max="1" width="24.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>text</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Experienced team</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Modern technology</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Direct communication</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>End-to-end development</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
   <cols>
@@ -801,362 +1042,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
-  <cols>
-    <col min="1" max="1" width="13.83203125" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>icon</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Astro</v>
-      </c>
-      <c r="B2" t="str">
-        <v>astro.svg</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Vue</v>
-      </c>
-      <c r="B3" t="str">
-        <v>vue.svg</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>React</v>
-      </c>
-      <c r="B4" t="str">
-        <v>react.svg</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TypeScript</v>
-      </c>
-      <c r="B5" t="str">
-        <v>typeScript.svg</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Tailwindcss</v>
-      </c>
-      <c r="B6" t="str">
-        <v>tailwindcss.svg</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Next</v>
-      </c>
-      <c r="B7" t="str">
-        <v>next.svg</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Nodejs</v>
-      </c>
-      <c r="B8" t="str">
-        <v>nodejs.svg</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>HTML5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>HTML5.svg</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>CSS3</v>
-      </c>
-      <c r="B10" t="str">
-        <v>CSS3.svg</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>JavaScript</v>
-      </c>
-      <c r="B11" t="str">
-        <v>javaScript.svg</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Git</v>
-      </c>
-      <c r="B12" t="str">
-        <v>git.svg</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Supabase</v>
-      </c>
-      <c r="B13" t="str">
-        <v>supabase.svg</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Mysql</v>
-      </c>
-      <c r="B14" t="str">
-        <v>mysql.svg</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Bash</v>
-      </c>
-      <c r="B15" t="str">
-        <v>bash.svg</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="40.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>item</v>
-      </c>
-      <c r="C1" t="str">
-        <v>icon</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Web Development</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Single Page Applications (SPAs)</v>
-      </c>
-      <c r="C2" t="str">
-        <v>web</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Web Development</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Landing pages and business websites</v>
-      </c>
-      <c r="C3" t="str">
-        <v>web</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Web Development</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Portfolio websites</v>
-      </c>
-      <c r="C4" t="str">
-        <v>web</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Mobile Development</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Mobile-friendly web apps</v>
-      </c>
-      <c r="C5" t="str">
-        <v>mobile</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Mobile Development</v>
-      </c>
-      <c r="B6" t="str">
-        <v>React Native mobile apps</v>
-      </c>
-      <c r="C6" t="str">
-        <v>mobile</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>UI/UX Design &amp; Prototyping</v>
-      </c>
-      <c r="B7" t="str">
-        <v>UI design with Figma &amp; Canva</v>
-      </c>
-      <c r="C7" t="str">
-        <v>design</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>UI/UX Design &amp; Prototyping</v>
-      </c>
-      <c r="B8" t="str">
-        <v>UX research &amp; improvements</v>
-      </c>
-      <c r="C8" t="str">
-        <v>design</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>UI/UX Design &amp; Prototyping</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Prototyping for websites &amp; mobile apps</v>
-      </c>
-      <c r="C9" t="str">
-        <v>design</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="63.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>title</v>
-      </c>
-      <c r="B1" t="str">
-        <v>status</v>
-      </c>
-      <c r="C1" t="str">
-        <v>image</v>
-      </c>
-      <c r="D1" t="str">
-        <v>github</v>
-      </c>
-      <c r="E1" t="str">
-        <v>preview</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Project One</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Deployed</v>
-      </c>
-      <c r="C2" t="str">
-        <v>https://placehold.co/600x400/1a1a1a/ffffff?text=Project+One</v>
-      </c>
-      <c r="D2" t="str">
-        <v>https://github.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>#!</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Project Two</v>
-      </c>
-      <c r="B3" t="str">
-        <v>On Development</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://placehold.co/600x400/1a1a1a/ffffff?text=Project+Two</v>
-      </c>
-      <c r="D3" t="str">
-        <v>https://github.com</v>
-      </c>
-      <c r="E3" t="str">
-        <v>#!</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Project Three</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Contributor</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://placehold.co/600x400/1a1a1a/ffffff?text=Project+Three</v>
-      </c>
-      <c r="D4" t="str">
-        <v>https://github.com</v>
-      </c>
-      <c r="E4" t="str">
-        <v>#!</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Project Four</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Deployed</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://placehold.co/600x400/1a1a1a/ffffff?text=Project+Four</v>
-      </c>
-      <c r="D5" t="str">
-        <v>https://github.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>#!</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
@@ -1187,29 +1075,18 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Styled with</v>
+        <v>Content from</v>
       </c>
       <c r="B3" t="str">
-        <v>CSS</v>
+        <v>Excel</v>
       </c>
       <c r="C3" t="str">
-        <v>CSS3.svg</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Content from</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Excel</v>
-      </c>
-      <c r="C4" t="str">
         <v>git.svg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>